--- a/public/planilhas/05_precificacao.xlsx
+++ b/public/planilhas/05_precificacao.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRECO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEU_TEMPO" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -20,9 +20,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; h&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +33,40 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00C99C66"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000A1322"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="008593A8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="000A1322"/>
       <sz val="18"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="008593A8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
       <name val="Calibri"/>
-      <color rgb="005C6B82"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -46,17 +74,8 @@
       <color rgb="000A1322"/>
       <sz val="14"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -65,7 +84,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F1EA"/>
+        <fgColor rgb="000A1322"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8F4EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,7 +99,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A1322"/>
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,38 +123,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -195,6 +239,115 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Preço por cenário</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!C11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$A$12:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$C$12:$C$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -486,207 +639,240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trust Excel · Precificação de Serviço</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TRUST EXCEL  ·  TRUST CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3 cenários automáticos: mínimo / ideal / premium</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+          <t>Dashboard de Precificação</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>3 cenários automáticos com margem saudável</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Serviço</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Consultoria / projeto sob demanda</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Horas estimadas</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Custos variáveis da entrega</t>
-        </is>
-      </c>
       <c r="B6" s="5" t="n">
-        <v>450</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Valor da hora (automático)</t>
-        </is>
-      </c>
-      <c r="B7" s="5">
-        <f>MEU_TEMPO!B8</f>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Custos variáveis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Valor da hora</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
+        <f>MEU_TEMPO!B9</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Custo total da entrega</t>
-        </is>
-      </c>
-      <c r="B8" s="5">
-        <f>(B5*B7)+B6</f>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Custo total</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>(B6*B8)+B7</f>
         <v/>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Cenário</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Margem</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Preço sugerido</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Quando usar</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Faixa visual</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Mínimo</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B12" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="C11" s="5">
-        <f>$B$8/(1-B11)</f>
+      <c r="C12" s="10">
+        <f>$B$9/(1-B12)</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Entrar na conta / baixa complexidade</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="E12" s="5">
+        <f>REPT("█",ROUND(B12*20,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Ideal</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B13" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="C12" s="5">
-        <f>$B$8/(1-B12)</f>
+      <c r="C13" s="11">
+        <f>$B$9/(1-B13)</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Padrão saudável de operação</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="E13" s="5">
+        <f>REPT("█",ROUND(B13*20,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B14" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="C13" s="5">
-        <f>$B$8/(1-B13)</f>
+      <c r="C14" s="12">
+        <f>$B$9/(1-B14)</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Urgência, especialização ou alto risco</t>
         </is>
       </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Regra de desconto: não baixe preço — remova escopo. Horas a remover para um preço-alvo:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="E14" s="5">
+        <f>REPT("█",ROUND(B14*20,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Preço-alvo do cliente</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Horas máximas para fechar</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
-        <f>MAX(0,((B16*(1-0.3))-B6)/B7)</f>
+      <c r="B28" s="6" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Horas máximas p/ fechar (margem ideal 30%)</t>
+        </is>
+      </c>
+      <c r="B29" s="14">
+        <f>MAX(0,((B28*(1-0.3))-B7)/B8)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Automação TrustCorp: altere renda, horas e custos — todos os preços recalculam.</t>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Regra TrustCorp: não baixe preço — remova escopo. A planilha mostra quantas horas cortar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -696,82 +882,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trust Excel · Valor da Hora</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TRUST EXCEL  ·  TRUST CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Valor da Hora</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>Base automática da precificação</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Renda desejada / mês</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="B5" s="16" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Custos fixos mensais</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B6" s="16" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Horas produtivas / mês</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B7" s="17" t="n">
         <v>110</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Valor da sua hora</t>
-        </is>
-      </c>
-      <c r="B8" s="12">
-        <f>(B4+B5)/B6</f>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>VALOR DA SUA HORA</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>(B5+B6)/B7</f>
         <v/>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Dica: use 100–120h produtivas, não 160h. Honestidade aqui evita preço suicida.</t>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Use 100–120h produtivas, não 160h. Honestidade aqui evita preço suicida.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
